--- a/test/fixtures/manual-calc.xlsx
+++ b/test/fixtures/manual-calc.xlsx
@@ -420,6 +420,7 @@
       </c>
       <c r="C2">
         <f>A2*B2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -431,6 +432,7 @@
       </c>
       <c r="C3">
         <f>A3*B3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
